--- a/供应明细.xlsx
+++ b/供应明细.xlsx
@@ -1,14 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Web\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEA7079-4897-4169-A467-B6B903C435EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21550" windowHeight="10080" activeTab="3"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原始数据" sheetId="1" r:id="rId1"/>
-    <sheet name="录课改进的供应数据" sheetId="2" r:id="rId2"/>
+    <sheet name="供应数据" sheetId="2" r:id="rId2"/>
     <sheet name="供应商表" sheetId="3" r:id="rId3"/>
     <sheet name="设备零件表" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="5" r:id="rId5"/>
@@ -747,18 +753,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -781,159 +781,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -958,194 +807,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1168,251 +831,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1445,61 +866,17 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1786,18 +1163,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C112"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="28.8727272727273" customWidth="1"/>
-    <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="4.75454545454545" customWidth="1"/>
+    <col min="1" max="1" width="28.90625" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="4.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3034,23 +2411,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E121"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.0909090909091" customWidth="1"/>
-    <col min="2" max="2" width="36.8181818181818" customWidth="1"/>
-    <col min="3" max="3" width="28.3636363636364" customWidth="1"/>
-    <col min="4" max="4" width="13.1818181818182" customWidth="1"/>
+    <col min="1" max="1" width="15.08984375" customWidth="1"/>
+    <col min="2" max="2" width="36.81640625" customWidth="1"/>
+    <col min="3" max="3" width="28.36328125" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" spans="1:5">
+    <row r="1" spans="1:5" ht="17">
       <c r="A1" s="4" t="s">
         <v>79</v>
       </c>
@@ -3067,7 +2442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:5">
+    <row r="2" spans="1:5" ht="34">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -3084,7 +2459,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:5">
+    <row r="3" spans="1:5" ht="34">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -3101,7 +2476,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="17" spans="1:5">
+    <row r="4" spans="1:5" ht="34">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -3118,7 +2493,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:5">
+    <row r="5" spans="1:5" ht="34">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -3135,7 +2510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:5">
+    <row r="6" spans="1:5" ht="34">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -3152,7 +2527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="17" spans="1:5">
+    <row r="7" spans="1:5" ht="34">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -3169,7 +2544,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:5">
+    <row r="8" spans="1:5" ht="34">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3186,7 +2561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:5">
+    <row r="9" spans="1:5" ht="34">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3203,7 +2578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="17" spans="1:5">
+    <row r="10" spans="1:5" ht="34">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3220,7 +2595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" ht="17" spans="1:5">
+    <row r="11" spans="1:5" ht="34">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3237,7 +2612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="17" spans="1:5">
+    <row r="12" spans="1:5" ht="34">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3254,7 +2629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="1:5">
+    <row r="13" spans="1:5" ht="34">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3271,7 +2646,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:5">
+    <row r="14" spans="1:5" ht="17">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3288,7 +2663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:5">
+    <row r="15" spans="1:5" ht="17">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3305,7 +2680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="17" spans="1:5">
+    <row r="16" spans="1:5" ht="17">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3322,7 +2697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="17" spans="1:5">
+    <row r="17" spans="1:5" ht="17">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3339,7 +2714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="17" spans="1:5">
+    <row r="18" spans="1:5" ht="17">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3356,7 +2731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:5">
+    <row r="19" spans="1:5" ht="17">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -3373,7 +2748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" ht="17" spans="1:5">
+    <row r="20" spans="1:5" ht="17">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3390,7 +2765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="17" spans="1:5">
+    <row r="21" spans="1:5" ht="17">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3407,7 +2782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" ht="17" spans="1:5">
+    <row r="22" spans="1:5" ht="17">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3424,7 +2799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="1:5">
+    <row r="23" spans="1:5" ht="17">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3441,7 +2816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" ht="17" spans="1:5">
+    <row r="24" spans="1:5" ht="17">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3458,7 +2833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="17" spans="1:5">
+    <row r="25" spans="1:5" ht="17">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3475,7 +2850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="17" spans="1:5">
+    <row r="26" spans="1:5" ht="17">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3492,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="17" spans="1:5">
+    <row r="27" spans="1:5" ht="17">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3509,7 +2884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" ht="17" spans="1:5">
+    <row r="28" spans="1:5" ht="17">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3526,7 +2901,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" ht="17" spans="1:5">
+    <row r="29" spans="1:5" ht="17">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3543,7 +2918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="17" spans="1:5">
+    <row r="30" spans="1:5" ht="17">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3560,7 +2935,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" ht="17" spans="1:5">
+    <row r="31" spans="1:5" ht="17">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3577,7 +2952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" ht="17" spans="1:5">
+    <row r="32" spans="1:5" ht="17">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3594,7 +2969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" ht="17" spans="1:5">
+    <row r="33" spans="1:5" ht="17">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3611,7 +2986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="17" spans="1:5">
+    <row r="34" spans="1:5" ht="17">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3628,7 +3003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" ht="17" spans="1:5">
+    <row r="35" spans="1:5" ht="17">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3645,7 +3020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="17" spans="1:5">
+    <row r="36" spans="1:5" ht="17">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3662,7 +3037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="17" spans="1:5">
+    <row r="37" spans="1:5" ht="17">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3679,7 +3054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" ht="17" spans="1:5">
+    <row r="38" spans="1:5" ht="17">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3696,7 +3071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="17" spans="1:5">
+    <row r="39" spans="1:5" ht="17">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3713,7 +3088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" ht="17" spans="1:5">
+    <row r="40" spans="1:5" ht="17">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3730,7 +3105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" ht="17" spans="1:5">
+    <row r="41" spans="1:5" ht="17">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3747,7 +3122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="17" spans="1:5">
+    <row r="42" spans="1:5" ht="17">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -3764,7 +3139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" ht="17" spans="1:5">
+    <row r="43" spans="1:5" ht="17">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3781,7 +3156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="17" spans="1:5">
+    <row r="44" spans="1:5" ht="17">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -3798,7 +3173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" ht="17" spans="1:5">
+    <row r="45" spans="1:5" ht="17">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3815,7 +3190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" ht="17" spans="1:5">
+    <row r="46" spans="1:5" ht="17">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -3832,7 +3207,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" ht="17" spans="1:5">
+    <row r="47" spans="1:5" ht="17">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -3849,7 +3224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" ht="17" spans="1:5">
+    <row r="48" spans="1:5" ht="17">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -3866,7 +3241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" ht="17" spans="1:5">
+    <row r="49" spans="1:5" ht="17">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -3883,7 +3258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" ht="17" spans="1:5">
+    <row r="50" spans="1:5" ht="17">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -3900,7 +3275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" ht="17" spans="1:5">
+    <row r="51" spans="1:5" ht="17">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -3917,7 +3292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" ht="17" spans="1:5">
+    <row r="52" spans="1:5" ht="17">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -3934,7 +3309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" ht="17" spans="1:5">
+    <row r="53" spans="1:5" ht="17">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -3951,7 +3326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" ht="17" spans="1:5">
+    <row r="54" spans="1:5" ht="17">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -3968,7 +3343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" ht="17" spans="1:5">
+    <row r="55" spans="1:5" ht="17">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -3985,7 +3360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" ht="17" spans="1:5">
+    <row r="56" spans="1:5" ht="17">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -4002,7 +3377,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" ht="17" spans="1:5">
+    <row r="57" spans="1:5" ht="17">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -4019,7 +3394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" ht="17" spans="1:5">
+    <row r="58" spans="1:5" ht="17">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -4036,7 +3411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" ht="17" spans="1:5">
+    <row r="59" spans="1:5" ht="17">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -4053,7 +3428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" ht="17" spans="1:5">
+    <row r="60" spans="1:5" ht="17">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -4070,7 +3445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" ht="17" spans="1:5">
+    <row r="61" spans="1:5" ht="17">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -4087,7 +3462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" ht="17" spans="1:5">
+    <row r="62" spans="1:5" ht="17">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -4104,7 +3479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" ht="17" spans="1:5">
+    <row r="63" spans="1:5" ht="17">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -4121,7 +3496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" ht="17" spans="1:5">
+    <row r="64" spans="1:5" ht="17">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -4138,7 +3513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" ht="17" spans="1:5">
+    <row r="65" spans="1:5" ht="17">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -4155,7 +3530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" ht="17" spans="1:5">
+    <row r="66" spans="1:5" ht="17">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -4172,7 +3547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" ht="17" spans="1:5">
+    <row r="67" spans="1:5" ht="17">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -4189,7 +3564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" ht="17" spans="1:5">
+    <row r="68" spans="1:5" ht="17">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -4206,7 +3581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" ht="17" spans="1:5">
+    <row r="69" spans="1:5" ht="17">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -4223,7 +3598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" ht="17" spans="1:5">
+    <row r="70" spans="1:5" ht="17">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -4240,7 +3615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" ht="17" spans="1:5">
+    <row r="71" spans="1:5" ht="17">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -4257,7 +3632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" ht="17" spans="1:5">
+    <row r="72" spans="1:5" ht="17">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -4274,7 +3649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" ht="17" spans="1:5">
+    <row r="73" spans="1:5" ht="17">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -4291,7 +3666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" ht="17" spans="1:5">
+    <row r="74" spans="1:5" ht="17">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -4308,7 +3683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" ht="17" spans="1:5">
+    <row r="75" spans="1:5" ht="17">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -4325,7 +3700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" ht="17" spans="1:5">
+    <row r="76" spans="1:5" ht="17">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -4342,7 +3717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" ht="17" spans="1:5">
+    <row r="77" spans="1:5" ht="17">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -4359,7 +3734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" ht="17" spans="1:5">
+    <row r="78" spans="1:5" ht="17">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -4376,7 +3751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" ht="17" spans="1:5">
+    <row r="79" spans="1:5" ht="17">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -4393,7 +3768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" ht="17" spans="1:5">
+    <row r="80" spans="1:5" ht="17">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -4410,7 +3785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" ht="17" spans="1:5">
+    <row r="81" spans="1:5" ht="17">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -4427,7 +3802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" ht="17" spans="1:5">
+    <row r="82" spans="1:5" ht="17">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -4444,7 +3819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" ht="17" spans="1:5">
+    <row r="83" spans="1:5" ht="17">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -4461,7 +3836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" ht="17" spans="1:5">
+    <row r="84" spans="1:5" ht="17">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -4478,7 +3853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" ht="17" spans="1:5">
+    <row r="85" spans="1:5" ht="17">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -4495,7 +3870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" ht="17" spans="1:5">
+    <row r="86" spans="1:5" ht="17">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -4512,7 +3887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" ht="17" spans="1:5">
+    <row r="87" spans="1:5" ht="17">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -4529,7 +3904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" ht="17" spans="1:5">
+    <row r="88" spans="1:5" ht="17">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -4546,7 +3921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" ht="17" spans="1:5">
+    <row r="89" spans="1:5" ht="17">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -4563,7 +3938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" ht="17" spans="1:5">
+    <row r="90" spans="1:5" ht="17">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -4580,7 +3955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" ht="17" spans="1:5">
+    <row r="91" spans="1:5" ht="17">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -4597,7 +3972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" ht="17" spans="1:5">
+    <row r="92" spans="1:5" ht="17">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -4614,7 +3989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" ht="17" spans="1:5">
+    <row r="93" spans="1:5" ht="17">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -4631,7 +4006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" ht="17" spans="1:5">
+    <row r="94" spans="1:5" ht="17">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -4648,7 +4023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" ht="17" spans="1:5">
+    <row r="95" spans="1:5" ht="17">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -4665,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" ht="17" spans="1:5">
+    <row r="96" spans="1:5" ht="17">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -4682,7 +4057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" ht="17" spans="1:5">
+    <row r="97" spans="1:5" ht="17">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -4699,7 +4074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" ht="17" spans="1:5">
+    <row r="98" spans="1:5" ht="17">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -4716,7 +4091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" ht="17" spans="1:5">
+    <row r="99" spans="1:5" ht="17">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -4733,7 +4108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" ht="17" spans="1:5">
+    <row r="100" spans="1:5" ht="17">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -4750,7 +4125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" ht="17" spans="1:5">
+    <row r="101" spans="1:5" ht="17">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -4767,7 +4142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" ht="17" spans="1:5">
+    <row r="102" spans="1:5" ht="17">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -4784,7 +4159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" ht="17" spans="1:5">
+    <row r="103" spans="1:5" ht="17">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -4801,7 +4176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" ht="17" spans="1:5">
+    <row r="104" spans="1:5" ht="17">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -4818,7 +4193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" ht="17" spans="1:5">
+    <row r="105" spans="1:5" ht="17">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -4835,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" ht="17" spans="1:5">
+    <row r="106" spans="1:5" ht="17">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -4852,7 +4227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" ht="17" spans="1:5">
+    <row r="107" spans="1:5" ht="17">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -4869,7 +4244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" ht="17" spans="1:5">
+    <row r="108" spans="1:5" ht="17">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -4886,7 +4261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" ht="17" spans="1:5">
+    <row r="109" spans="1:5" ht="17">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -4903,7 +4278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" ht="17" spans="1:5">
+    <row r="110" spans="1:5" ht="17">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -4920,7 +4295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" ht="17" spans="1:5">
+    <row r="111" spans="1:5" ht="17">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -4937,7 +4312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" ht="17" spans="1:5">
+    <row r="112" spans="1:5" ht="17">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -4954,7 +4329,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" ht="17" spans="1:5">
+    <row r="113" spans="1:5" ht="17">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -4971,7 +4346,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" ht="17" spans="1:5">
+    <row r="114" spans="1:5" ht="17">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -4988,7 +4363,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" ht="17" spans="1:5">
+    <row r="115" spans="1:5" ht="17">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -5005,7 +4380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" ht="17" spans="1:5">
+    <row r="116" spans="1:5" ht="17">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -5022,7 +4397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" ht="17" spans="1:5">
+    <row r="117" spans="1:5" ht="17">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -5039,7 +4414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" ht="17" spans="1:5">
+    <row r="118" spans="1:5" ht="17">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -5056,7 +4431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" ht="17" spans="1:5">
+    <row r="119" spans="1:5" ht="17">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -5073,7 +4448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" ht="17" spans="1:5">
+    <row r="120" spans="1:5" ht="17">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -5090,7 +4465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" ht="17" spans="1:5">
+    <row r="121" spans="1:5" ht="17">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -5109,20 +4484,18 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="38.1818181818182" customWidth="1"/>
+    <col min="2" max="2" width="38.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29" spans="1:4">
+    <row r="1" spans="1:4" ht="34">
       <c r="A1" s="4" t="s">
         <v>89</v>
       </c>
@@ -5136,7 +4509,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" ht="19" customHeight="1" spans="1:4">
+    <row r="2" spans="1:4" ht="19" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>93</v>
       </c>
@@ -5150,7 +4523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:4">
+    <row r="3" spans="1:4" ht="34">
       <c r="A3" s="3" t="s">
         <v>95</v>
       </c>
@@ -5164,7 +4537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="17" spans="1:4">
+    <row r="4" spans="1:4" ht="34">
       <c r="A4" s="3" t="s">
         <v>97</v>
       </c>
@@ -5178,7 +4551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:4">
+    <row r="5" spans="1:4" ht="34">
       <c r="A5" s="3" t="s">
         <v>98</v>
       </c>
@@ -5192,7 +4565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:4">
+    <row r="6" spans="1:4" ht="34">
       <c r="A6" s="3" t="s">
         <v>99</v>
       </c>
@@ -5206,7 +4579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" ht="17" spans="1:4">
+    <row r="7" spans="1:4" ht="34">
       <c r="A7" s="3" t="s">
         <v>100</v>
       </c>
@@ -5220,7 +4593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:4">
+    <row r="8" spans="1:4" ht="34">
       <c r="A8" s="3" t="s">
         <v>101</v>
       </c>
@@ -5234,7 +4607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:4">
+    <row r="9" spans="1:4" ht="14" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>102</v>
       </c>
@@ -5248,7 +4621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:4">
+    <row r="10" spans="1:4" ht="14" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>103</v>
       </c>
@@ -5262,7 +4635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:4">
+    <row r="11" spans="1:4" ht="14" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>105</v>
       </c>
@@ -5276,7 +4649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:4">
+    <row r="12" spans="1:4" ht="14" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>107</v>
       </c>
@@ -5290,7 +4663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:4">
+    <row r="13" spans="1:4" ht="14" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>109</v>
       </c>
@@ -5304,7 +4677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:4">
+    <row r="14" spans="1:4" ht="14" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>111</v>
       </c>
@@ -5318,7 +4691,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:4">
+    <row r="15" spans="1:4" ht="14" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>113</v>
       </c>
@@ -5334,24 +4707,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D73"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.2727272727273" customWidth="1"/>
+    <col min="1" max="1" width="20.26953125" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="35.2727272727273" customWidth="1"/>
-    <col min="4" max="4" width="28.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="35.5454545454545" customWidth="1"/>
+    <col min="3" max="3" width="35.26953125" customWidth="1"/>
+    <col min="4" max="4" width="28.6328125" customWidth="1"/>
+    <col min="5" max="5" width="35.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:4">
+    <row r="1" spans="1:4" ht="17">
       <c r="A1" s="1" t="s">
         <v>115</v>
       </c>
@@ -5365,7 +4736,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" ht="17" spans="1:4">
+    <row r="2" spans="1:4" ht="17">
       <c r="A2" s="2" t="s">
         <v>119</v>
       </c>
@@ -5379,7 +4750,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:4">
+    <row r="3" spans="1:4" ht="17">
       <c r="A3" s="2" t="s">
         <v>121</v>
       </c>
@@ -5393,7 +4764,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" ht="17" spans="1:4">
+    <row r="4" spans="1:4" ht="17">
       <c r="A4" s="2" t="s">
         <v>123</v>
       </c>
@@ -5407,7 +4778,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:4">
+    <row r="5" spans="1:4" ht="17">
       <c r="A5" s="2" t="s">
         <v>125</v>
       </c>
@@ -5421,7 +4792,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:4">
+    <row r="6" spans="1:4" ht="17">
       <c r="A6" s="2" t="s">
         <v>127</v>
       </c>
@@ -5435,7 +4806,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" ht="17" spans="1:4">
+    <row r="7" spans="1:4" ht="17">
       <c r="A7" s="2" t="s">
         <v>128</v>
       </c>
@@ -5449,7 +4820,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:4">
+    <row r="8" spans="1:4" ht="17">
       <c r="A8" s="2" t="s">
         <v>130</v>
       </c>
@@ -5463,7 +4834,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:4">
+    <row r="9" spans="1:4" ht="17">
       <c r="A9" s="2" t="s">
         <v>133</v>
       </c>
@@ -5477,7 +4848,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="10" ht="17" spans="1:4">
+    <row r="10" spans="1:4" ht="17">
       <c r="A10" s="2" t="s">
         <v>135</v>
       </c>
@@ -5491,7 +4862,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="11" ht="17" spans="1:4">
+    <row r="11" spans="1:4" ht="17">
       <c r="A11" s="2" t="s">
         <v>137</v>
       </c>
@@ -5505,7 +4876,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" ht="17" spans="1:4">
+    <row r="12" spans="1:4" ht="17">
       <c r="A12" s="2" t="s">
         <v>139</v>
       </c>
@@ -5519,7 +4890,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="1:4">
+    <row r="13" spans="1:4" ht="17">
       <c r="A13" s="2" t="s">
         <v>141</v>
       </c>
@@ -5533,7 +4904,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:4">
+    <row r="14" spans="1:4" ht="17">
       <c r="A14" s="2" t="s">
         <v>143</v>
       </c>
@@ -5547,7 +4918,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:4">
+    <row r="15" spans="1:4" ht="17">
       <c r="A15" s="2" t="s">
         <v>144</v>
       </c>
@@ -5561,7 +4932,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" ht="17" spans="1:4">
+    <row r="16" spans="1:4" ht="17">
       <c r="A16" s="2" t="s">
         <v>145</v>
       </c>
@@ -5575,7 +4946,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" ht="17" spans="1:4">
+    <row r="17" spans="1:4" ht="17">
       <c r="A17" s="2" t="s">
         <v>147</v>
       </c>
@@ -5589,7 +4960,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="18" ht="17" spans="1:4">
+    <row r="18" spans="1:4" ht="17">
       <c r="A18" s="2" t="s">
         <v>149</v>
       </c>
@@ -5603,7 +4974,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:4">
+    <row r="19" spans="1:4" ht="17">
       <c r="A19" s="2" t="s">
         <v>151</v>
       </c>
@@ -5617,7 +4988,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="20" ht="17" spans="1:4">
+    <row r="20" spans="1:4" ht="17">
       <c r="A20" s="2" t="s">
         <v>153</v>
       </c>
@@ -5631,7 +5002,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="21" ht="17" spans="1:4">
+    <row r="21" spans="1:4" ht="17">
       <c r="A21" s="2" t="s">
         <v>155</v>
       </c>
@@ -5645,7 +5016,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="22" ht="17" spans="1:4">
+    <row r="22" spans="1:4" ht="17">
       <c r="A22" s="2" t="s">
         <v>156</v>
       </c>
@@ -5659,7 +5030,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="1:4">
+    <row r="23" spans="1:4" ht="17">
       <c r="A23" s="2" t="s">
         <v>157</v>
       </c>
@@ -5673,7 +5044,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="24" ht="17" spans="1:4">
+    <row r="24" spans="1:4" ht="17">
       <c r="A24" s="2" t="s">
         <v>158</v>
       </c>
@@ -5687,7 +5058,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" ht="17" spans="1:4">
+    <row r="25" spans="1:4" ht="17">
       <c r="A25" s="2" t="s">
         <v>160</v>
       </c>
@@ -5701,7 +5072,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" ht="17" spans="1:4">
+    <row r="26" spans="1:4" ht="17">
       <c r="A26" s="2" t="s">
         <v>161</v>
       </c>
@@ -5715,7 +5086,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="27" ht="17" spans="1:4">
+    <row r="27" spans="1:4" ht="17">
       <c r="A27" s="2" t="s">
         <v>162</v>
       </c>
@@ -5729,7 +5100,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="28" ht="17" spans="1:4">
+    <row r="28" spans="1:4" ht="17">
       <c r="A28" s="2" t="s">
         <v>163</v>
       </c>
@@ -5743,7 +5114,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" ht="17" spans="1:4">
+    <row r="29" spans="1:4" ht="17">
       <c r="A29" s="2" t="s">
         <v>165</v>
       </c>
@@ -5757,7 +5128,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="30" ht="17" spans="1:4">
+    <row r="30" spans="1:4" ht="17">
       <c r="A30" s="2" t="s">
         <v>167</v>
       </c>
@@ -5771,7 +5142,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="31" ht="17" spans="1:4">
+    <row r="31" spans="1:4" ht="17">
       <c r="A31" s="2" t="s">
         <v>169</v>
       </c>
@@ -5785,7 +5156,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="32" ht="17" spans="1:4">
+    <row r="32" spans="1:4" ht="17">
       <c r="A32" s="2" t="s">
         <v>171</v>
       </c>
@@ -5799,7 +5170,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="33" ht="17" spans="1:4">
+    <row r="33" spans="1:4" ht="17">
       <c r="A33" s="2" t="s">
         <v>173</v>
       </c>
@@ -5813,7 +5184,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="34" ht="17" spans="1:4">
+    <row r="34" spans="1:4" ht="17">
       <c r="A34" s="2" t="s">
         <v>174</v>
       </c>
@@ -5827,7 +5198,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="35" ht="17" spans="1:4">
+    <row r="35" spans="1:4" ht="17">
       <c r="A35" s="2" t="s">
         <v>175</v>
       </c>
@@ -5841,7 +5212,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" ht="17" spans="1:4">
+    <row r="36" spans="1:4" ht="17">
       <c r="A36" s="2" t="s">
         <v>176</v>
       </c>
@@ -5855,7 +5226,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="37" ht="17" spans="1:4">
+    <row r="37" spans="1:4" ht="17">
       <c r="A37" s="2" t="s">
         <v>178</v>
       </c>
@@ -5869,7 +5240,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="38" ht="17" spans="1:4">
+    <row r="38" spans="1:4" ht="17">
       <c r="A38" s="2" t="s">
         <v>179</v>
       </c>
@@ -5883,7 +5254,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="39" ht="17" spans="1:4">
+    <row r="39" spans="1:4" ht="17">
       <c r="A39" s="2" t="s">
         <v>180</v>
       </c>
@@ -5897,7 +5268,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="40" ht="17" spans="1:4">
+    <row r="40" spans="1:4" ht="17">
       <c r="A40" s="2" t="s">
         <v>181</v>
       </c>
@@ -5911,7 +5282,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" ht="17" spans="1:4">
+    <row r="41" spans="1:4" ht="17">
       <c r="A41" s="2" t="s">
         <v>183</v>
       </c>
@@ -5925,7 +5296,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="42" ht="17" spans="1:4">
+    <row r="42" spans="1:4" ht="17">
       <c r="A42" s="2" t="s">
         <v>184</v>
       </c>
@@ -5939,7 +5310,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="43" ht="17" spans="1:4">
+    <row r="43" spans="1:4" ht="17">
       <c r="A43" s="2" t="s">
         <v>185</v>
       </c>
@@ -5953,7 +5324,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="44" ht="17" spans="1:4">
+    <row r="44" spans="1:4" ht="17">
       <c r="A44" s="2" t="s">
         <v>186</v>
       </c>
@@ -5967,7 +5338,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="45" ht="17" spans="1:4">
+    <row r="45" spans="1:4" ht="17">
       <c r="A45" s="2" t="s">
         <v>188</v>
       </c>
@@ -5981,7 +5352,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="46" ht="17" spans="1:4">
+    <row r="46" spans="1:4" ht="17">
       <c r="A46" s="2" t="s">
         <v>189</v>
       </c>
@@ -5995,7 +5366,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" ht="17" spans="1:4">
+    <row r="47" spans="1:4" ht="17">
       <c r="A47" s="2" t="s">
         <v>191</v>
       </c>
@@ -6009,7 +5380,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" ht="17" spans="1:4">
+    <row r="48" spans="1:4" ht="17">
       <c r="A48" s="2" t="s">
         <v>192</v>
       </c>
@@ -6023,7 +5394,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" ht="17" spans="1:4">
+    <row r="49" spans="1:4" ht="17">
       <c r="A49" s="2" t="s">
         <v>193</v>
       </c>
@@ -6037,7 +5408,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" ht="17" spans="1:4">
+    <row r="50" spans="1:4" ht="17">
       <c r="A50" s="2" t="s">
         <v>194</v>
       </c>
@@ -6051,7 +5422,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="51" ht="17" spans="1:4">
+    <row r="51" spans="1:4" ht="17">
       <c r="A51" s="3" t="s">
         <v>195</v>
       </c>
@@ -6065,7 +5436,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="52" ht="17" spans="1:4">
+    <row r="52" spans="1:4" ht="17">
       <c r="A52" s="3" t="s">
         <v>196</v>
       </c>
@@ -6079,7 +5450,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="53" ht="17" spans="1:4">
+    <row r="53" spans="1:4" ht="17">
       <c r="A53" s="3" t="s">
         <v>197</v>
       </c>
@@ -6093,7 +5464,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" ht="17" spans="1:4">
+    <row r="54" spans="1:4" ht="17">
       <c r="A54" s="3" t="s">
         <v>198</v>
       </c>
@@ -6107,7 +5478,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="55" ht="17" spans="1:4">
+    <row r="55" spans="1:4" ht="17">
       <c r="A55" s="3" t="s">
         <v>199</v>
       </c>
@@ -6121,7 +5492,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" ht="17" spans="1:4">
+    <row r="56" spans="1:4" ht="17">
       <c r="A56" s="3" t="s">
         <v>201</v>
       </c>
@@ -6135,7 +5506,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57" ht="17" spans="1:4">
+    <row r="57" spans="1:4" ht="17">
       <c r="A57" s="3" t="s">
         <v>202</v>
       </c>
@@ -6149,7 +5520,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="58" ht="17" spans="1:4">
+    <row r="58" spans="1:4" ht="17">
       <c r="A58" s="3" t="s">
         <v>203</v>
       </c>
@@ -6163,7 +5534,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="59" ht="17" spans="1:4">
+    <row r="59" spans="1:4" ht="17">
       <c r="A59" s="3" t="s">
         <v>204</v>
       </c>
@@ -6177,7 +5548,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="60" ht="17" spans="1:4">
+    <row r="60" spans="1:4" ht="17">
       <c r="A60" s="3" t="s">
         <v>205</v>
       </c>
@@ -6191,7 +5562,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="61" ht="17" spans="1:4">
+    <row r="61" spans="1:4" ht="17">
       <c r="A61" s="3" t="s">
         <v>206</v>
       </c>
@@ -6205,7 +5576,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" ht="17" spans="1:4">
+    <row r="62" spans="1:4" ht="17">
       <c r="A62" s="3" t="s">
         <v>208</v>
       </c>
@@ -6219,7 +5590,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" ht="17" spans="1:4">
+    <row r="63" spans="1:4" ht="17">
       <c r="A63" s="3" t="s">
         <v>210</v>
       </c>
@@ -6233,7 +5604,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" ht="17" spans="1:4">
+    <row r="64" spans="1:4" ht="17">
       <c r="A64" s="3" t="s">
         <v>212</v>
       </c>
@@ -6247,7 +5618,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="65" ht="17" spans="1:4">
+    <row r="65" spans="1:4" ht="17">
       <c r="A65" s="3" t="s">
         <v>214</v>
       </c>
@@ -6261,7 +5632,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="66" ht="17" spans="1:4">
+    <row r="66" spans="1:4" ht="17">
       <c r="A66" s="3" t="s">
         <v>216</v>
       </c>
@@ -6275,7 +5646,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="67" ht="17" spans="1:4">
+    <row r="67" spans="1:4" ht="17">
       <c r="A67" s="3" t="s">
         <v>217</v>
       </c>
@@ -6289,7 +5660,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="68" ht="17" spans="1:4">
+    <row r="68" spans="1:4" ht="17">
       <c r="A68" s="3" t="s">
         <v>219</v>
       </c>
@@ -6303,7 +5674,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="69" ht="17" spans="1:4">
+    <row r="69" spans="1:4" ht="17">
       <c r="A69" s="3" t="s">
         <v>220</v>
       </c>
@@ -6317,7 +5688,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="70" ht="17" spans="1:4">
+    <row r="70" spans="1:4" ht="17">
       <c r="A70" s="3" t="s">
         <v>223</v>
       </c>
@@ -6331,7 +5702,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="71" ht="17" spans="1:4">
+    <row r="71" spans="1:4" ht="17">
       <c r="A71" s="3" t="s">
         <v>226</v>
       </c>
@@ -6345,7 +5716,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="72" ht="17" spans="1:4">
+    <row r="72" spans="1:4" ht="17">
       <c r="A72" s="3" t="s">
         <v>230</v>
       </c>
@@ -6359,7 +5730,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" ht="17" spans="1:4">
+    <row r="73" spans="1:4" ht="17">
       <c r="A73" s="3" t="s">
         <v>233</v>
       </c>
@@ -6375,17 +5746,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>